--- a/RBI02.xlsx
+++ b/RBI02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="64">
   <si>
     <t/>
   </si>
@@ -184,22 +184,10 @@
     <t>OLAH APEL FJ SUN PCS</t>
   </si>
   <si>
-    <t>20111863</t>
-  </si>
-  <si>
-    <t>OLAH APL FJ RYL  PCS</t>
-  </si>
-  <si>
     <t>10027546</t>
   </si>
   <si>
     <t>ANGGUR REDFEL WHL</t>
-  </si>
-  <si>
-    <t>20111860</t>
-  </si>
-  <si>
-    <t>OLAH ANGGUR RED WHL</t>
   </si>
   <si>
     <t>20112666</t>
@@ -607,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1069,16 +1057,16 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>59</v>
       </c>
@@ -1089,66 +1077,26 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E27" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/RBI02.xlsx
+++ b/RBI02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="64">
   <si>
     <t/>
   </si>
@@ -595,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -603,10 +603,11 @@
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="5" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -625,8 +626,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -642,11 +649,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -662,11 +669,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -682,11 +689,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -702,11 +709,11 @@
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -722,11 +729,11 @@
       <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -742,11 +749,11 @@
       <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -762,11 +769,11 @@
       <c r="E8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
@@ -782,11 +789,11 @@
       <c r="E9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
@@ -802,11 +809,11 @@
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -822,11 +829,11 @@
       <c r="E11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -842,11 +849,11 @@
       <c r="E12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
@@ -862,11 +869,11 @@
       <c r="E13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -882,11 +889,11 @@
       <c r="E14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
@@ -902,11 +909,11 @@
       <c r="E15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>41</v>
       </c>
@@ -922,11 +929,11 @@
       <c r="E16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>43</v>
       </c>
@@ -942,11 +949,11 @@
       <c r="E17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>45</v>
       </c>
@@ -962,11 +969,11 @@
       <c r="E18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>48</v>
       </c>
@@ -982,11 +989,11 @@
       <c r="E19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>51</v>
       </c>
@@ -1002,11 +1009,11 @@
       <c r="E20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>53</v>
       </c>
@@ -1022,11 +1029,11 @@
       <c r="E21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>55</v>
       </c>
@@ -1042,11 +1049,11 @@
       <c r="E22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>57</v>
       </c>
@@ -1062,7 +1069,7 @@
       <c r="E23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/RBI02.xlsx
+++ b/RBI02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="64">
   <si>
     <t/>
   </si>
@@ -595,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -603,11 +603,10 @@
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="5" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -626,14 +625,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -649,11 +642,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -669,11 +662,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -689,11 +682,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -709,11 +702,11 @@
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -729,11 +722,11 @@
       <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -749,11 +742,11 @@
       <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -769,11 +762,11 @@
       <c r="E8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
@@ -789,11 +782,11 @@
       <c r="E9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
@@ -809,11 +802,11 @@
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -829,11 +822,11 @@
       <c r="E11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -849,11 +842,11 @@
       <c r="E12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
@@ -869,11 +862,11 @@
       <c r="E13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -889,11 +882,11 @@
       <c r="E14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
@@ -909,11 +902,11 @@
       <c r="E15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>41</v>
       </c>
@@ -929,11 +922,11 @@
       <c r="E16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>43</v>
       </c>
@@ -949,11 +942,11 @@
       <c r="E17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>45</v>
       </c>
@@ -969,11 +962,11 @@
       <c r="E18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>48</v>
       </c>
@@ -989,11 +982,11 @@
       <c r="E19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>51</v>
       </c>
@@ -1009,11 +1002,11 @@
       <c r="E20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>53</v>
       </c>
@@ -1029,11 +1022,11 @@
       <c r="E21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>55</v>
       </c>
@@ -1049,11 +1042,11 @@
       <c r="E22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>57</v>
       </c>
@@ -1069,7 +1062,7 @@
       <c r="E23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/RBI02.xlsx
+++ b/RBI02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="68">
   <si>
     <t/>
   </si>
@@ -172,22 +172,34 @@
     <t>JRK MURCOT/WOKAM PCS</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>20076891</t>
   </si>
   <si>
     <t>JERUK KINO PCS</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>20111854</t>
   </si>
   <si>
     <t>OLAH APEL FJ SUN PCS</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>10027546</t>
   </si>
   <si>
     <t>ANGGUR REDFEL WHL</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>20112666</t>
@@ -997,10 +1009,10 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1008,19 +1020,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1028,19 +1040,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>16</v>
@@ -1048,19 +1060,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1068,16 +1080,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>4</v>
@@ -1085,16 +1097,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>8</v>

--- a/RBI02.xlsx
+++ b/RBI02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="65">
   <si>
     <t/>
   </si>
@@ -155,15 +155,6 @@
   </si>
   <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>20131590</t>
-  </si>
-  <si>
-    <t>LENGKENG BKK  PCK</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
   <si>
     <t>20087711</t>
@@ -607,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1035,7 +1026,7 @@
         <v>56</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1055,10 +1046,10 @@
         <v>59</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>60</v>
       </c>
@@ -1069,13 +1060,10 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1089,26 +1077,9 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="1" t="s">
         <v>8</v>
       </c>
     </row>
